--- a/staff_forms/003_employee_monitoring_consent_form--staff_forms.xlsx
+++ b/staff_forms/003_employee_monitoring_consent_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>employee_monitoring_consent_form_employee_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee</t>
+          <t>Employee Monitoring Consent Form Employee 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1148,189 +1148,189 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_5_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_11_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_12_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_12_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_18_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,58 +1347,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_18_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_19_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_19_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_23_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,24 +1415,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_23_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_24_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
+          <t>employee_monitoring_consent_form_employee_24_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1458,91 +1458,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>monitoring_activities_related_to:_"employee_monitoring_consent_form"</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Monitoring activities related to: "Employee Monitoring Consent Form"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>employee_monitoring_consent_form_employee_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
